--- a/PS05/data/Complaints_Output.xlsx
+++ b/PS05/data/Complaints_Output.xlsx
@@ -1,71 +1,486 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
+  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+  <x:bookViews>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="0" activeTab="0"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Complaints_Report" sheetId="2" r:id="rId4"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="162913"/>
+  <x:extLst>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Complaint_ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Citizen_Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Original_Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Classified_Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Submission_Channel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Complaint_Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date_Received</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Date_Formatted</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t>text</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>C001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Thabo Mokoena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Water</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Burst pipe near my house</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Processed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Naledi Dlamini</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Electricity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Load shedding not on schedule</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sibusiso Nkosi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Refuse</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PDF Form</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bin not collected this week</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ayesha Khan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Other</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Street light not working</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Johan van Wyk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No water supply since yesterday</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Zanele Ndlovu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Transformer exploded in my street</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rubbish piling up on street corner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potholes on main road</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Low water pressure in my area</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No power for 3 days</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Refuse truck missed our block</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Illegal dumping near park</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-09-12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12 September 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-08-21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21 August 2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C032</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C037</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C039</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C044</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C050</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="0" formatCode=""/>
+  </x:numFmts>
+  <x:fonts count="2" x14ac:knownFonts="1">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="2">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </x:cellStyleXfs>
+  <x:cellXfs count="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+    </x:ext>
+  </x:extLst>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +745,1542 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1"/>
+  <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <x:sheetData/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:I52"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" spans="1:9">
+      <x:c r="A1" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
+      <x:c r="A2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
+      <x:c r="A3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
+      <x:c r="A9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
+      <x:c r="A10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
+      <x:c r="A12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
+      <x:c r="A13" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
+      <x:c r="A14" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
+      <x:c r="A15" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
+      <x:c r="A16" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
+      <x:c r="A17" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
+      <x:c r="A18" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
+      <x:c r="A19" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
+      <x:c r="A20" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
+      <x:c r="A21" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
+      <x:c r="A22" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
+      <x:c r="A23" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
+      <x:c r="A24" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
+      <x:c r="A25" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
+      <x:c r="A26" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
+      <x:c r="A27" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
+      <x:c r="A28" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
+      <x:c r="A29" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
+      <x:c r="A30" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
+      <x:c r="A31" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
+      <x:c r="A32" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
+      <x:c r="A33" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E33" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F33" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
+      <x:c r="A34" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E34" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F34" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
+      <x:c r="A35" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E35" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
+      <x:c r="A36" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E36" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F36" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
+      <x:c r="A37" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E37" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F37" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
+      <x:c r="A38" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E38" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F38" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
+      <x:c r="A39" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E39" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F39" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
+      <x:c r="A40" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E40" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F40" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
+      <x:c r="A41" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
+      <x:c r="A42" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
+      <x:c r="A43" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
+      <x:c r="A44" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
+      <x:c r="A45" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
+      <x:c r="A46" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
+      <x:c r="A47" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
+      <x:c r="A48" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
+      <x:c r="A49" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
+      <x:c r="A50" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E50" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F50" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
+      <x:c r="A51" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E51" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F51" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
+      <x:c r="A52" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E52" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F52" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>